--- a/Plan_RM_comunas_por_completar.xlsx
+++ b/Plan_RM_comunas_por_completar.xlsx
@@ -288,7 +288,7 @@
     <t>Av. Américo Vespucio Norte 1090, oficina 201, Vitacura,Región Metropolitana</t>
   </si>
   <si>
-    <t>G3 · Resto de la cartera</t>
+    <t>G3 · Clientes retail</t>
   </si>
   <si>
     <t>IOPA</t>
